--- a/artfynd/A 43369-2024 artfynd.xlsx
+++ b/artfynd/A 43369-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>73983354</v>
       </c>
       <c r="B2" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107283</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445521.1234669399</v>
+        <v>445521</v>
       </c>
       <c r="R2" t="n">
-        <v>6299229.718351005</v>
+        <v>6299230</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1978-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74149942</v>
       </c>
       <c r="B3" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445521.1234669399</v>
+        <v>445521</v>
       </c>
       <c r="R3" t="n">
-        <v>6299229.718351005</v>
+        <v>6299230</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -870,19 +850,9 @@
           <t>1978-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -926,12 +896,7 @@
         <v>74768830</v>
       </c>
       <c r="B4" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445521.1234669399</v>
+        <v>445521</v>
       </c>
       <c r="R4" t="n">
-        <v>6299229.718351005</v>
+        <v>6299230</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -996,19 +961,9 @@
           <t>1978-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 43369-2024 artfynd.xlsx
+++ b/artfynd/A 43369-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983354</v>
       </c>
       <c r="B2" t="n">
-        <v>107283</v>
+        <v>107292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74149942</v>
       </c>
       <c r="B3" t="n">
-        <v>98508</v>
+        <v>98511</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74768830</v>
       </c>
       <c r="B4" t="n">
-        <v>98625</v>
+        <v>98628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43369-2024 artfynd.xlsx
+++ b/artfynd/A 43369-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983354</v>
       </c>
       <c r="B2" t="n">
-        <v>107292</v>
+        <v>107297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74149942</v>
       </c>
       <c r="B3" t="n">
-        <v>98511</v>
+        <v>98512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74768830</v>
       </c>
       <c r="B4" t="n">
-        <v>98628</v>
+        <v>98629</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43369-2024 artfynd.xlsx
+++ b/artfynd/A 43369-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983354</v>
       </c>
       <c r="B2" t="n">
-        <v>107297</v>
+        <v>107325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74149942</v>
       </c>
       <c r="B3" t="n">
-        <v>98512</v>
+        <v>98539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74768830</v>
       </c>
       <c r="B4" t="n">
-        <v>98629</v>
+        <v>98656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43369-2024 artfynd.xlsx
+++ b/artfynd/A 43369-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983354</v>
       </c>
       <c r="B2" t="n">
-        <v>107325</v>
+        <v>107331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74149942</v>
       </c>
       <c r="B3" t="n">
-        <v>98539</v>
+        <v>98545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74768830</v>
       </c>
       <c r="B4" t="n">
-        <v>98656</v>
+        <v>98662</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43369-2024 artfynd.xlsx
+++ b/artfynd/A 43369-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983354</v>
       </c>
       <c r="B2" t="n">
-        <v>107353</v>
+        <v>107358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74149942</v>
       </c>
       <c r="B3" t="n">
-        <v>98566</v>
+        <v>98571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74768830</v>
       </c>
       <c r="B4" t="n">
-        <v>98683</v>
+        <v>98688</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43369-2024 artfynd.xlsx
+++ b/artfynd/A 43369-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983354</v>
       </c>
       <c r="B2" t="n">
-        <v>107358</v>
+        <v>107366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74149942</v>
       </c>
       <c r="B3" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74768830</v>
       </c>
       <c r="B4" t="n">
-        <v>98688</v>
+        <v>98696</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43369-2024 artfynd.xlsx
+++ b/artfynd/A 43369-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983354</v>
       </c>
       <c r="B2" t="n">
-        <v>107366</v>
+        <v>107376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74149942</v>
       </c>
       <c r="B3" t="n">
-        <v>98579</v>
+        <v>98589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74768830</v>
       </c>
       <c r="B4" t="n">
-        <v>98696</v>
+        <v>98706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43369-2024 artfynd.xlsx
+++ b/artfynd/A 43369-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73983354</v>
+        <v>74768830</v>
       </c>
       <c r="B2" t="n">
-        <v>107376</v>
+        <v>99156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219955</v>
+        <v>219875</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5D0j 2013. SOM: Arnica montana. LEG: Ingvar Christoffersson</t>
+          <t>Smålands flora 2007: KOO: 5D0j 2013. SOM: Platanthera chlorantha. LEG: Ingvar Christoffersson</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,30 +786,34 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74149942</v>
+        <v>73983354</v>
       </c>
       <c r="B3" t="n">
-        <v>98589</v>
+        <v>107907</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223597</v>
+        <v>219955</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -857,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5D0j 2013. SOM: Dactylorhiza maculata ssp. maculata. LEG: Ingvar Christoffersson</t>
+          <t>Smålands flora 2007: KOO: 5D0j 2013. SOM: Arnica montana. LEG: Ingvar Christoffersson</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74768830</v>
+        <v>74149942</v>
       </c>
       <c r="B4" t="n">
-        <v>98706</v>
+        <v>99038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,23 +908,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219875</v>
+        <v>223597</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5D0j 2013. SOM: Platanthera chlorantha. LEG: Ingvar Christoffersson</t>
+          <t>Smålands flora 2007: KOO: 5D0j 2013. SOM: Dactylorhiza maculata ssp. maculata. LEG: Ingvar Christoffersson</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 43369-2024 artfynd.xlsx
+++ b/artfynd/A 43369-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74768830</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73983354</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,8 +1016,18 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74149942</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>